--- a/app/uploads/Template_Catatan_Transaksi_Harian - usahaku.xlsx
+++ b/app/uploads/Template_Catatan_Transaksi_Harian - usahaku.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DD6026-D3F3-471D-B196-56BF0543D479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68ED141-9A9A-47EA-805C-1E0BEBDACD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,12 +121,6 @@
     </r>
   </si>
   <si>
-    <t>Nama Usaha : PT. Mekar Sari</t>
-  </si>
-  <si>
-    <t>Catatan Bulan :  November 2025</t>
-  </si>
-  <si>
     <t>Modal</t>
   </si>
   <si>
@@ -158,6 +152,12 @@
   </si>
   <si>
     <t>pembelian barang</t>
+  </si>
+  <si>
+    <t>Nama Usaha : PT. Jaya maju</t>
+  </si>
+  <si>
+    <t>Catatan Bulan : Juli 2023</t>
   </si>
 </sst>
 </file>
@@ -718,7 +718,7 @@
     </row>
     <row r="4" spans="4:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="E4" s="15" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F4" s="15"/>
       <c r="I4" s="17" t="s">
@@ -731,7 +731,7 @@
     </row>
     <row r="5" spans="4:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E5" s="15" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F5" s="15"/>
       <c r="I5" s="19" t="s">
@@ -786,10 +786,10 @@
         <v>45668</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9" s="8">
         <v>1900000</v>
@@ -805,10 +805,10 @@
         <v>45668</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" s="8">
         <v>700000</v>
@@ -824,10 +824,10 @@
         <v>45699</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G11" s="8">
         <v>400000</v>
@@ -843,10 +843,10 @@
         <v>45699</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G12" s="8">
         <v>100000</v>
@@ -862,10 +862,10 @@
         <v>45727</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G13" s="8">
         <v>300000</v>
@@ -881,10 +881,10 @@
         <v>45727</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" s="8">
         <v>150000</v>
@@ -900,10 +900,10 @@
         <v>45758</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G15" s="8">
         <v>1000000</v>
@@ -919,10 +919,10 @@
         <v>45758</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16" s="8">
         <v>400000</v>
@@ -938,10 +938,10 @@
         <v>45788</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G17" s="8">
         <v>800000</v>
@@ -957,10 +957,10 @@
         <v>45788</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G18" s="8">
         <v>500000</v>
@@ -976,10 +976,10 @@
         <v>45819</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G19" s="8">
         <v>200000</v>
@@ -990,10 +990,10 @@
         <v>45819</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G20" s="8">
         <v>900000</v>
